--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/04-tareas-brigada-creativa.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/04-tareas-brigada-creativa.xlsx
@@ -1,22 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chef Ejecutivo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sous-Chef" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Partida Caliente" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Partida Fría" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Chef Pastelero" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sumiller" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Maître-Sala" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chef Ejecutivo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sous-Chef" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partida Caliente" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partida Fría" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chef Pastelero" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sumiller" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maître-Sala" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Chef Ejecutivo'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Sous-Chef'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Partida Caliente'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Partida Fría'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Chef Pastelero'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Sumiller'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Maître-Sala'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -24,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +93,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="11">
@@ -173,66 +186,77 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="10" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -592,15 +616,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -608,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -643,9 +669,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -688,8 +712,25 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -698,18 +739,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -726,6 +767,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -940,6 +982,26 @@
       <c r="E14" s="12" t="n"/>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(E6:E14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B6:B14,"?*")</f>
+        <v>9.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
@@ -963,12 +1025,26 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -977,18 +1053,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1005,6 +1081,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1219,6 +1296,26 @@
       <c r="E14" s="12" t="n"/>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(E6:E14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B6:B14,"?*")</f>
+        <v>9.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
@@ -1242,12 +1339,26 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1256,18 +1367,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1284,6 +1395,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1460,6 +1572,26 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")</f>
+        <v>7.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
@@ -1483,12 +1615,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1497,18 +1643,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1525,6 +1671,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1701,6 +1848,26 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")</f>
+        <v>7.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
@@ -1724,12 +1891,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1738,18 +1919,18 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1766,6 +1947,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1980,6 +2162,26 @@
       <c r="E14" s="12" t="n"/>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(E6:E14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B6:B14,"?*")</f>
+        <v>9.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
@@ -2003,12 +2205,26 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2017,18 +2233,18 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2045,6 +2261,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2221,6 +2438,26 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")</f>
+        <v>7.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
@@ -2244,12 +2481,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2258,18 +2509,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2286,6 +2537,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2444,6 +2696,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2601,6 +2854,26 @@
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C21">
+        <f>COUNTIF(E6:E20,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>COUNTIF(B6:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
@@ -2625,11 +2898,25 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/04-tareas-brigada-creativa.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/04-tareas-brigada-creativa.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -716,7 +716,14 @@
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -990,7 +997,7 @@
         </is>
       </c>
       <c r="C15">
-        <f>COUNTIF(E6:E14,"✓")</f>
+        <f>COUNTIFS(B6:B14,"?*",E6:E14,"✓")-COUNTIFS(B6:B14,"Tarea",E6:E14,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -999,7 +1006,7 @@
         </is>
       </c>
       <c r="E15">
-        <f>COUNTIF(B6:B14,"?*")</f>
+        <f>COUNTIF(B6:B14,"?*")-COUNTIF(B6:B14,"Tarea")-COUNTIF(E6:E14,"N/A")</f>
         <v>9.0</v>
       </c>
     </row>
@@ -1031,8 +1038,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1304,7 +1311,7 @@
         </is>
       </c>
       <c r="C15">
-        <f>COUNTIF(E6:E14,"✓")</f>
+        <f>COUNTIFS(B6:B14,"?*",E6:E14,"✓")-COUNTIFS(B6:B14,"Tarea",E6:E14,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -1313,7 +1320,7 @@
         </is>
       </c>
       <c r="E15">
-        <f>COUNTIF(B6:B14,"?*")</f>
+        <f>COUNTIF(B6:B14,"?*")-COUNTIF(B6:B14,"Tarea")-COUNTIF(E6:E14,"N/A")</f>
         <v>9.0</v>
       </c>
     </row>
@@ -1345,8 +1352,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1580,7 +1587,7 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(E6:E12,"✓")</f>
+        <f>COUNTIFS(B6:B12,"?*",E6:E12,"✓")-COUNTIFS(B6:B12,"Tarea",E6:E12,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1589,7 +1596,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>COUNTIF(B6:B12,"?*")</f>
+        <f>COUNTIF(B6:B12,"?*")-COUNTIF(B6:B12,"Tarea")-COUNTIF(E6:E12,"N/A")</f>
         <v>7.0</v>
       </c>
     </row>
@@ -1621,8 +1628,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1741,7 +1748,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Ceviches y tartares: cortar máx. 2h antes de servicio</t>
+          <t>Ceviches y tartares: cortar máx. 2 h antes del servicio y SÓLO con pescado que haya pasado la congelación preventiva frente al ANISAKIS (ver 02 · «Pre-elab Día»)</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1779,7 +1786,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Marinados rápidos (cítricos, vinagres)</t>
+          <t>Marinados rápidos (cítricos, vinagres): el ácido NO mata el anisakis ni sustituye a la congelación previa — sólo cambia la textura</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1856,7 +1863,7 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(E6:E12,"✓")</f>
+        <f>COUNTIFS(B6:B12,"?*",E6:E12,"✓")-COUNTIFS(B6:B12,"Tarea",E6:E12,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1865,7 +1872,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>COUNTIF(B6:B12,"?*")</f>
+        <f>COUNTIF(B6:B12,"?*")-COUNTIF(B6:B12,"Tarea")-COUNTIF(E6:E12,"N/A")</f>
         <v>7.0</v>
       </c>
     </row>
@@ -1897,8 +1904,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2170,7 +2177,7 @@
         </is>
       </c>
       <c r="C15">
-        <f>COUNTIF(E6:E14,"✓")</f>
+        <f>COUNTIFS(B6:B14,"?*",E6:E14,"✓")-COUNTIFS(B6:B14,"Tarea",E6:E14,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -2179,7 +2186,7 @@
         </is>
       </c>
       <c r="E15">
-        <f>COUNTIF(B6:B14,"?*")</f>
+        <f>COUNTIF(B6:B14,"?*")-COUNTIF(B6:B14,"Tarea")-COUNTIF(E6:E14,"N/A")</f>
         <v>9.0</v>
       </c>
     </row>
@@ -2211,8 +2218,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2446,7 +2453,7 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(E6:E12,"✓")</f>
+        <f>COUNTIFS(B6:B12,"?*",E6:E12,"✓")-COUNTIFS(B6:B12,"Tarea",E6:E12,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -2455,7 +2462,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>COUNTIF(B6:B12,"?*")</f>
+        <f>COUNTIF(B6:B12,"?*")-COUNTIF(B6:B12,"Tarea")-COUNTIF(E6:E12,"N/A")</f>
         <v>7.0</v>
       </c>
     </row>
@@ -2487,8 +2494,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2862,8 +2869,8 @@
         </is>
       </c>
       <c r="C21">
-        <f>COUNTIF(E6:E20,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B20,"?*",E6:E20,"✓")-COUNTIFS(B6:B20,"Tarea",E6:E20,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,8 +2878,8 @@
         </is>
       </c>
       <c r="E21">
-        <f>COUNTIF(B6:B20,"?*")</f>
-        <v>13.0</v>
+        <f>COUNTIF(B6:B20,"?*")-COUNTIF(B6:B20,"Tarea")-COUNTIF(E6:E20,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
     <row r="22">
@@ -2904,8 +2911,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
